--- a/assets/tools_template.xlsx
+++ b/assets/tools_template.xlsx
@@ -62,7 +62,7 @@
     <t>对讲机</t>
   </si>
   <si>
-    <t>便携式孔探仪（确保充满电）</t>
+    <t>便携式孔探仪</t>
   </si>
   <si>
     <t>红外温度仪</t>

--- a/assets/tools_template.xlsx
+++ b/assets/tools_template.xlsx
@@ -62,10 +62,10 @@
     <t>对讲机</t>
   </si>
   <si>
-    <t>便携式孔探仪</t>
-  </si>
-  <si>
-    <t>红外温度仪</t>
+    <t>孔探仪</t>
+  </si>
+  <si>
+    <t>温度计</t>
   </si>
   <si>
     <t>力矩扳手1-5NM</t>
